--- a/artfynd/A 53764-2022 artfynd.xlsx
+++ b/artfynd/A 53764-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125744182</v>
       </c>
       <c r="B2" t="n">
-        <v>108873</v>
+        <v>108880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53764-2022 artfynd.xlsx
+++ b/artfynd/A 53764-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125744182</v>
       </c>
       <c r="B2" t="n">
-        <v>108880</v>
+        <v>108883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53764-2022 artfynd.xlsx
+++ b/artfynd/A 53764-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125744182</v>
       </c>
       <c r="B2" t="n">
-        <v>108883</v>
+        <v>108887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53764-2022 artfynd.xlsx
+++ b/artfynd/A 53764-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125744182</v>
       </c>
       <c r="B2" t="n">
-        <v>108887</v>
+        <v>108888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53764-2022 artfynd.xlsx
+++ b/artfynd/A 53764-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125744182</v>
       </c>
       <c r="B2" t="n">
-        <v>108888</v>
+        <v>108890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53764-2022 artfynd.xlsx
+++ b/artfynd/A 53764-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125744182</v>
       </c>
       <c r="B2" t="n">
-        <v>108890</v>
+        <v>108892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53764-2022 artfynd.xlsx
+++ b/artfynd/A 53764-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125744182</v>
       </c>
       <c r="B2" t="n">
-        <v>108892</v>
+        <v>108896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53764-2022 artfynd.xlsx
+++ b/artfynd/A 53764-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125744182</v>
       </c>
       <c r="B2" t="n">
-        <v>108896</v>
+        <v>108909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53764-2022 artfynd.xlsx
+++ b/artfynd/A 53764-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125744182</v>
       </c>
       <c r="B2" t="n">
-        <v>108909</v>
+        <v>108912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
